--- a/naver-place-crawler/results_nail/기장군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/기장군_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빈s magic</t>
+          <t>정관 민뷰티크</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>overcome6@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1359-6914</t>
+          <t>0507-1357-3978</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로 63 1층 빈s magic</t>
+          <t>부산광역시 기장군 정관읍 정관로 545 홈플러스 정문 바로맞은편 길가</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/min._.boutique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1527971991</t>
+          <t>1517396176</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527971991</t>
+          <t>https://m.place.naver.com/place/1517396176</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>정관 아린네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h7292uj@naver.com</t>
+          <t>lla0020@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-724-8232</t>
+          <t>051-727-1544</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
+          <t>부산광역시 기장군 정관읍 정관로 485 롯데캐슬프라자</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h7292uj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>283</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16855482</t>
+          <t>1312537670</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16855482</t>
+          <t>https://m.place.naver.com/place/1312537670</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일, 살랑</t>
+          <t>코델리아진네일뷰티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>blackholecd@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-5811</t>
+          <t>0507-1316-8137</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동3로 54-4 1층 네일, 살랑</t>
+          <t>부산광역시 기장군 기장읍 기장해안로 98 C211호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxfxfxoK</t>
+          <t>https://open.kakao.com/o/sbFNXENb</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1311109904</t>
+          <t>1451145377</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311109904</t>
+          <t>https://m.place.naver.com/place/1451145377</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,20 +846,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수진네일아트</t>
+          <t>네일스케치</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>linnii@naver.com</t>
+          <t>kongdw@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>051-724-3373</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
+          <t>부산광역시 기장군 기장읍 차성동로 73</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1769136676</t>
+          <t>31517196</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769136676</t>
+          <t>https://m.place.naver.com/place/31517196</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -936,24 +940,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일경</t>
+          <t>빈s magic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>overcome6@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1392-1745</t>
+          <t>0507-1359-6914</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 322동103호</t>
+          <t>부산광역시 기장군 기장읍 차성남로 63 1층 빈s magic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1047568389</t>
+          <t>1527971991</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1047568389</t>
+          <t>https://m.place.naver.com/place/1527971991</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>네일,만나</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>ehgptn321@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1376-6218</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전로 79 1층 102호</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s4fI6Dug</t>
+          <t>https://open.kakao.com/o/s1IMEHUc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026985488</t>
+          <t>1996364380</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026985488</t>
+          <t>https://m.place.naver.com/place/1996364380</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>정관 아린네일</t>
+          <t>727nail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kitty8116@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>051-727-1544</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 485 롯데캐슬프라자</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 324동 108호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/727nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1152,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1177,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1312537670</t>
+          <t>2018352334</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312537670</t>
+          <t>https://m.place.naver.com/place/2018352334</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1214,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>숩네일</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyunjju1541@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1467-1273</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 기장대로 495 1층 107호</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 2 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_su.b_nail_</t>
+          <t>https://www.instagram.com/p/CSrI-pVFHtQ/?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,7 +1247,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1282,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1430742656</t>
+          <t>1586444618</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430742656</t>
+          <t>https://m.place.naver.com/place/1586444618</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1304,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BaRa네일샵</t>
+          <t>네일향</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>joen1204@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1325,7 +1317,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로288번길 22 1층 BaRa 네일샵</t>
+          <t>부산광역시 기장군 기장읍 차성남로65번길 11</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1365,13 +1357,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1766863509</t>
+          <t>19693133</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766863509</t>
+          <t>https://m.place.naver.com/place/19693133</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1394,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이지민네일</t>
+          <t>누아네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>cjfng@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1364-4182</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안전통상가 108-2호</t>
+          <t>부산광역시 기장군 정관읍 모전1길 9 102동 B103층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://instagram.com/wings_0331</t>
+          <t>https://www.instagram.com/nua_lashperm?igsh=N2xlN2JsMnBjNnQw</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1955852559</t>
+          <t>2022687189</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955852559</t>
+          <t>https://m.place.naver.com/place/2022687189</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1484,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>코델리아네일뷰티</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1336-8137</t>
+          <t>051-722-1551</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 41 아이프라자 1차 603호</t>
+          <t>부산광역시 기장군 일광읍 해빛5로 21-3 지음프라자 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_codellia.jin</t>
+          <t>https://www.instagram.com/nabi.nail_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1541,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1556,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1736623275</t>
+          <t>20557575</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1736623275</t>
+          <t>https://m.place.naver.com/place/20557575</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1578,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>더네일킹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>ovoa333@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1362-5752</t>
+          <t>0507-1391-3331</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동2길 24-7 리네일</t>
+          <t>부산광역시 기장군 정관읍 가동1길 11-5 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/the_nailking</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1622,7 +1610,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1643,17 +1631,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1105532713</t>
+          <t>1661274406</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105532713</t>
+          <t>https://m.place.naver.com/place/1661274406</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1672,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>동생네일</t>
+          <t>여우숲네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>umma_89@naver.com</t>
+          <t>hanna7342@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1376-6203</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡로 39 301동 1층 106-1호</t>
+          <t>부산광역시 기장군 기장읍 차성로332번길 14 여우숲 네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d.sang_nail</t>
+          <t>http://instagram.com/lovely_lail_6604</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1725,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1061297905</t>
+          <t>1249638908</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061297905</t>
+          <t>https://m.place.naver.com/place/1249638908</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1762,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>정관소노네일</t>
+          <t>코델리아네일뷰티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1789,18 +1773,18 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1390-5016</t>
+          <t>0507-1336-8137</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산2길 25-3 로얄하우스 1층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 41 아이프라자 1차 603호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sono_b.t</t>
+          <t>https://www.instagram.com/beauty_codellia.jin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1835,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1535038585</t>
+          <t>1736623275</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535038585</t>
+          <t>https://m.place.naver.com/place/1736623275</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1872,34 +1856,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>손끄치스치다</t>
+          <t>베스타네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>innazzang-@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1432-1235</t>
+          <t>0507-1398-1666</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 . 323동 107호</t>
+          <t>부산광역시 기장군 일광읍 해송4로 21 일광프라자 3층 304호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0701_a_reum/</t>
+          <t>https://open.kakao.com/me/vesta</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1920,7 +1904,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1913,13 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38479059</t>
+          <t>1527088754</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38479059</t>
+          <t>https://m.place.naver.com/place/1527088754</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1966,39 +1950,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일세르</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>noo_name_beauty@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1373-5187</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 산단4로 153-12 101호</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iaIZX/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2014,22 +1994,22 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2018,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2062927983</t>
+          <t>1133605184</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062927983</t>
+          <t>https://m.place.naver.com/place/1133605184</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2040,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>빛나담 뷰티테라스</t>
+          <t>더심플</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bitnadal_bt@naver.com</t>
+          <t>soyaa814@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1388-6656</t>
+          <t>0507-1404-8512</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 72 4층 401호</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 이지더원3차아파트 323동 2층 113호 더심플</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitnadam_bt</t>
+          <t>https://www.instagram.com/the.simple_nail?igsh=eHo2enB6MGZjNWQ0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1729711839</t>
+          <t>1926904977</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729711839</t>
+          <t>https://m.place.naver.com/place/1926904977</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2134,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일리쥬</t>
+          <t>네일홀릭</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dbdud0328@naver.com</t>
+          <t>minmin0319@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1384-0540</t>
+          <t>0507-1362-0848</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 213동 B206호</t>
+          <t>부산광역시 기장군 정관읍 달산길 22-11 1층 네일홀릭</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_leeju</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2186,7 +2166,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2202,22 +2182,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2206,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1360272320</t>
+          <t>1461860750</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1360272320</t>
+          <t>https://m.place.naver.com/place/1461860750</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2248,34 +2228,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일더예쁨</t>
+          <t>이지민네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>angpang8119@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1319-8116</t>
+          <t>0507-1364-4182</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로 160 2층 네일더예쁨</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안전통상가 108-2호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://clip.naver.com/yee_peumnail</t>
+          <t>http://instagram.com/wings_0331</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2305,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1502532902</t>
+          <t>1955852559</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1502532902</t>
+          <t>https://m.place.naver.com/place/1955852559</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2322,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>샐리 네일</t>
+          <t>네일샵끌리다</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>toy2968@naver.com</t>
+          <t>mame0508@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1383-5654</t>
+          <t>0507-1342-9503</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 40 정관신도시 현진에버빌 211호</t>
+          <t>부산광역시 기장군 일광읍 해빛2로 24 비스타동원1차상가 128호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sally_nail</t>
+          <t>https://blog.naver.com/mame0508</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2359,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1321337327</t>
+          <t>1462469485</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1321337327</t>
+          <t>https://m.place.naver.com/place/1462469485</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2436,34 +2416,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>검은고양이네일</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mmins-0610@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1320-6761</t>
+          <t>0507-1371-2638</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡로 29</t>
+          <t>부산광역시 기장군 정관읍 모전3길 43 102호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blackcat.mqpon.co.kr/</t>
+          <t>http://pf.kakao.com/_xkXxcqX/friend</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2484,22 +2464,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1921074769</t>
+          <t>2043055430</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1921074769</t>
+          <t>https://m.place.naver.com/place/2043055430</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2510,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H에스테틱</t>
+          <t>네일비</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>syuri__@naver.com</t>
+          <t>panic9861@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1406-3277</t>
+          <t>0507-1428-4178</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로182번길 9</t>
+          <t>부산광역시 기장군 기장읍 차성동로87번길 28 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_h</t>
+          <t>https://www.instagram.com/bs_nailbee?igsh=dnI4a2s5ZzJpMW10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2567,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1758643778</t>
+          <t>2039408171</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758643778</t>
+          <t>https://m.place.naver.com/place/2039408171</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2624,24 +2604,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>요니네일</t>
+          <t>은네일에스테틱</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yoni_nail@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1373-7728</t>
+          <t>0507-1368-7222</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로441번길 7 상가동 104호</t>
+          <t>부산광역시 기장군 기장읍 읍내로 122 2층 은네일&amp;에스테틱</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2681,13 +2661,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2676,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1905392632</t>
+          <t>1386160942</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1905392632</t>
+          <t>https://m.place.naver.com/place/1386160942</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2698,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제이밈네일</t>
+          <t>손끄치스치다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jaeny__@naver.com</t>
+          <t>innazzang-@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1472-4423</t>
+          <t>0507-1432-1235</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 122 103호</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 . 323동 107호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_mim_nail?igsh=bXdqZmVmcmxwNWcy</t>
+          <t>https://www.instagram.com/0701_a_reum/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2766,7 +2746,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2775,13 +2755,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1582950449</t>
+          <t>38479059</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1582950449</t>
+          <t>https://m.place.naver.com/place/38479059</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2792,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일,은</t>
+          <t>네일J</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>minukyung@naver.com</t>
+          <t>qpqptkfkd7@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1373-0854</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 383 대성타워빌딩 B103호</t>
+          <t>부산광역시 기장군 기장읍 차성로 305 1층 네일J</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.eun_/profilecard/?igsh=MXhid2VxMzVrdmMwYQ==</t>
+          <t>https://blog.naver.com/qpqptkfkd7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2849,7 +2825,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2869,13 +2845,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2860,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1799936115</t>
+          <t>1688859881</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799936115</t>
+          <t>https://m.place.naver.com/place/1688859881</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2906,29 +2882,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일홀릭</t>
+          <t>난달라</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>minmin0319@naver.com</t>
+          <t>nandala_nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1362-0848</t>
+          <t>0507-1406-0410</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산길 22-11 1층 네일홀릭</t>
+          <t>부산광역시 기장군 정관읍 구연방곡로 120 가화만사성더테라스1차302동108호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nandala_nail.0130</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2938,7 +2914,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2959,17 +2935,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>459</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2954,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1461860750</t>
+          <t>1874677609</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461860750</t>
+          <t>https://m.place.naver.com/place/1874677609</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3000,29 +2976,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>그녀, 빛나네일</t>
+          <t>에이치네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>usdbaoh24@naver.com</t>
+          <t>remon103@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1352-6632</t>
+          <t>0507-1308-6632</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관5로 12 상가226동 103호</t>
+          <t>부산광역시 기장군 정관읍 구연방곡로 10 정문상가104호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shesshining_nail?igsh=bDQ4eDh2cjZp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3032,7 +3008,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3053,17 +3029,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,17 +3048,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1874020835</t>
+          <t>1252239066</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874020835</t>
+          <t>https://m.place.naver.com/place/1252239066</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3094,29 +3070,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>정관마일리네일</t>
+          <t>봄봄</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tinda_com@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>bbpub@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ad@daangn.com</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1361-4832</t>
+          <t>0507-1365-7606</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 579 6층</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 11 104호 봄봄</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iGXxgC</t>
+          <t>https://www.daangn.com/kr/business-profiles/봄봄-23abca3f38a74635bf31eb721f6afc92</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3142,7 +3122,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3151,13 +3131,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1174</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1199</v>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1181950337</t>
+          <t>1754904846</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181950337</t>
+          <t>https://m.place.naver.com/place/1754904846</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3188,34 +3168,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뷰티샤네일</t>
+          <t>네일세르</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>daumi0820@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1354-4413</t>
+          <t>0507-1373-5187</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 213동 b201호</t>
+          <t>부산광역시 기장군 정관읍 산단4로 153-12 101호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautychanail</t>
+          <t>http://pf.kakao.com/_iaIZX/chat</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3236,7 +3216,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3245,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1573379404</t>
+          <t>2062927983</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573379404</t>
+          <t>https://m.place.naver.com/place/2062927983</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3282,25 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>여우숲네일</t>
+          <t>정관네일하러가</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hanna7342@naver.com</t>
+          <t>nailharuga@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1325-6461</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로332번길 14 여우숲 네일</t>
+          <t>부산광역시 기장군 정관읍 가동3로 24 서언빈 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/lovely_lail_6604</t>
+          <t>https://www.instagram.com/nailharuga</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3335,13 +3319,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>17</v>
+        <v>415</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R31" t="n">
-        <v>19</v>
+        <v>426</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1249638908</t>
+          <t>1972636570</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249638908</t>
+          <t>https://m.place.naver.com/place/1972636570</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3429,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3454,7 +3438,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>정관네일하러가</t>
+          <t>숩네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nailharuga@naver.com</t>
+          <t>hyunjju1541@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1325-6461</t>
+          <t>0507-1467-1273</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동3로 24 서언빈 1층</t>
+          <t>부산광역시 기장군 기장읍 기장대로 495 1층 107호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharuga</t>
+          <t>https://www.instagram.com/_su.b_nail_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3523,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="Q33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>426</v>
+        <v>89</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1972636570</t>
+          <t>1430742656</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972636570</t>
+          <t>https://m.place.naver.com/place/1430742656</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3560,25 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일앤아이래쉬</t>
+          <t>요니네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>naileyelashes@naver.com</t>
+          <t>yoni_nail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1373-7728</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관1로 18 126동 103호</t>
+          <t>부산광역시 기장군 기장읍 차성로441번길 7 상가동 104호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naileyelashes</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3588,12 +3576,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3613,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1000195214</t>
+          <t>1905392632</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000195214</t>
+          <t>https://m.place.naver.com/place/1905392632</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3650,29 +3638,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>찌니네일</t>
+          <t>네일경</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>js684177@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1472-5105</t>
+          <t>0507-1392-1745</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 305 1층</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 322동103호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zzini_nail_?igsh=MWRkd3o3amo5MHdkZQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,7 +3670,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3703,17 +3691,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3710,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2023205248</t>
+          <t>1047568389</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023205248</t>
+          <t>https://m.place.naver.com/place/1047568389</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3744,20 +3732,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일향</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>joen1204@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>051-728-3804</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로65번길 11</t>
+          <t>부산광역시 기장군 정관읍 정관7로 3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3797,13 +3789,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3804,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>19693133</t>
+          <t>32434749</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19693133</t>
+          <t>https://m.place.naver.com/place/32434749</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3826,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일밍</t>
+          <t>정관노바네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ksk98815@naver.com</t>
+          <t>angel9708@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3847,12 +3839,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 72 . 1층</t>
+          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ming1226</t>
+          <t>http://www.instagram.com/nova__beauty__</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3887,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>955</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3894,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1326191176</t>
+          <t>1011332772</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326191176</t>
+          <t>https://m.place.naver.com/place/1011332772</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3916,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>마이네일숍</t>
+          <t>BaRa네일샵</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hanzzang25@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3937,12 +3929,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 장안읍 길천길 15 1층 101호</t>
+          <t>부산광역시 기장군 기장읍 차성로288번길 22 1층 BaRa 네일샵</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mynailshop_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3952,7 +3944,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3973,17 +3965,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,17 +3984,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1576268118</t>
+          <t>1766863509</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576268118</t>
+          <t>https://m.place.naver.com/place/1766863509</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4006,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>연하뷰티네일</t>
+          <t>지유네일 기장일광점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4025,18 +4017,18 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1464-4702</t>
+          <t>0507-1359-9732</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-8 5층 502호</t>
+          <t>부산광역시 기장군 일광읍 이화로 7 2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailjiyu</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4046,7 +4038,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4067,17 +4059,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4078,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2067837278</t>
+          <t>1722948905</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067837278</t>
+          <t>https://m.place.naver.com/place/1722948905</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4100,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>리나운 뷰티가든</t>
+          <t>정숙한야시</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4117,20 +4109,16 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1442-7669</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로344번길 13 상가동 114호</t>
+          <t>부산광역시 기장군 기장읍 차성로441번길 7</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/renown_nail7667?igsh=MXhuaDBvYzJ4N3lhZQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4140,7 +4128,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4161,17 +4149,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1230254733</t>
+          <t>1074484941</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230254733</t>
+          <t>https://m.place.naver.com/place/1074484941</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4202,30 +4190,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>리아드네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>wpwlgus0219@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1304-6134</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 2 1층</t>
+          <t>부산광역시 기장군 기장읍 차성로 430 2층 208호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CSrI-pVFHtQ/?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/_y.liad_nail</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4235,7 +4227,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4255,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="R41" t="n">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,17 +4262,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1586444618</t>
+          <t>1202615718</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1586444618</t>
+          <t>https://m.place.naver.com/place/1202615718</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4292,29 +4284,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>남자다운네일 본점</t>
+          <t>검은고양이네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>mmins-0610@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>051-724-7396</t>
+          <t>0507-1320-6761</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로288번길 40</t>
+          <t>부산광역시 기장군 정관읍 방곡로 29</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blackcat.mqpon.co.kr/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4324,7 +4316,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4349,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R42" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,17 +4356,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1494717985</t>
+          <t>1921074769</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494717985</t>
+          <t>https://m.place.naver.com/place/1921074769</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4386,24 +4378,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에이치네일</t>
+          <t>네일봉봉</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>remon103@naver.com</t>
+          <t>ye0505@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1308-6632</t>
+          <t>0507-1310-0650</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 구연방곡로 10 정문상가104호</t>
+          <t>부산광역시 기장군 기장읍 대청로45번길 19 103호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4443,13 +4435,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,17 +4450,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1252239066</t>
+          <t>1569463367</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252239066</t>
+          <t>https://m.place.naver.com/place/1569463367</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4480,29 +4472,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에반뷰티</t>
+          <t>손톱</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>evan_b9@naver.com</t>
+          <t>gertrude01@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1342-7372</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로390번길 15 2층</t>
+          <t>부산광역시 기장군 정관읍 방곡3로 11 서희 스타힐스 상가동 102호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evan_beauty_/</t>
+          <t>http://instagram.com/sontob_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4537,13 +4525,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>287</v>
+        <v>27</v>
       </c>
       <c r="Q44" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>430</v>
+        <v>27</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,17 +4540,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1626526500</t>
+          <t>387880231</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626526500</t>
+          <t>https://m.place.naver.com/place/387880231</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4574,39 +4562,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>베스타네일</t>
+          <t>르포렘네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>leehw931222@naver.com</t>
+          <t>jiuhhuj@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1398-1666</t>
+          <t>0507-1496-3223</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송4로 21 일광프라자 3층 304호</t>
+          <t>부산광역시 기장군 정관읍 가동길 13-10 102호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/me/vesta</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4622,22 +4610,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Q45" t="n">
         <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,17 +4634,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1527088754</t>
+          <t>1097788106</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527088754</t>
+          <t>https://m.place.naver.com/place/1097788106</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4668,34 +4656,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엔포유온네일</t>
+          <t>네일더예쁨</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>paster33@naver.com</t>
+          <t>angpang8119@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1352-1221</t>
+          <t>0507-1319-8116</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛4로 1 B층 117호</t>
+          <t>부산광역시 기장군 기장읍 차성동로 160 2층 네일더예쁨</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n4u.on_nail</t>
+          <t>https://clip.naver.com/yee_peumnail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4725,13 +4713,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="R46" t="n">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4728,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2086668706</t>
+          <t>1502532902</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086668706</t>
+          <t>https://m.place.naver.com/place/1502532902</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4762,25 +4750,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일J</t>
+          <t>샐리 네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>qpqptkfkd7@naver.com</t>
+          <t>toy2968@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1383-5654</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 305 1층 네일J</t>
+          <t>부산광역시 기장군 정관읍 정관2로 40 정관신도시 현진에버빌 211호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qpqptkfkd7</t>
+          <t>https://www.instagram.com/_sally_nail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4795,7 +4787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4815,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="R47" t="n">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1688859881</t>
+          <t>1321337327</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688859881</t>
+          <t>https://m.place.naver.com/place/1321337327</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4852,25 +4844,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>신데렐라네일아트</t>
+          <t>도토리네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ellie2300@naver.com</t>
+          <t>tntpung@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1325-6971</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 철마면 고촌로28번길 3</t>
+          <t>부산광역시 기장군 정관읍 모전3길 31 1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/do.tori_nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4880,7 +4876,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4901,17 +4897,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4916,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1842273793</t>
+          <t>2083351756</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842273793</t>
+          <t>https://m.place.naver.com/place/2083351756</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4942,29 +4938,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일스케치</t>
+          <t>이안네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kongdw@naver.com</t>
+          <t>wendyandj@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>051-724-3373</t>
+          <t>0507-1307-2082</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로 73</t>
+          <t>부산광역시 기장군 기장읍 차성동로142번길 11 골든그린빌상가 B동 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/iann_nail</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4974,7 +4970,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4995,17 +4991,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +5010,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>31517196</t>
+          <t>1275481649</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31517196</t>
+          <t>https://m.place.naver.com/place/1275481649</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5036,29 +5032,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>난달라</t>
+          <t>동생네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nandala_nail@naver.com</t>
+          <t>umma_89@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1406-0410</t>
+          <t>0507-1376-6203</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 구연방곡로 120 가화만사성더테라스1차302동108호</t>
+          <t>부산광역시 기장군 정관읍 방곡로 39 301동 1층 106-1호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nandala_nail.0130</t>
+          <t>https://www.instagram.com/d.sang_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5093,13 +5089,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>428</v>
+        <v>32</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>458</v>
+        <v>33</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,17 +5104,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1874677609</t>
+          <t>1061297905</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874677609</t>
+          <t>https://m.place.naver.com/place/1061297905</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5130,29 +5126,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>모해, 네일앤뷰티</t>
+          <t>신데렐라네일아트</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>ellie2300@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>051-727-0080</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 581 성원프라자 116호 모해, 네일앤뷰티</t>
+          <t>부산광역시 기장군 철마면 고촌로28번길 3</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sukyung_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5162,7 +5154,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5183,17 +5175,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5194,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>30839584</t>
+          <t>1842273793</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30839584</t>
+          <t>https://m.place.naver.com/place/1842273793</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5224,29 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>지유네일 기장일광점</t>
+          <t>찌니네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>js684177@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1359-9732</t>
+          <t>0507-1472-5105</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 이화로 7 2층</t>
+          <t>부산광역시 기장군 기장읍 차성로 305 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailjiyu</t>
+          <t>https://www.instagram.com/zzini_nail_?igsh=MWRkd3o3amo5MHdkZQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5288,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1722948905</t>
+          <t>2023205248</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722948905</t>
+          <t>https://m.place.naver.com/place/2023205248</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5318,35 +5310,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일,만나</t>
+          <t>남자다운네일 본점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ehgptn321@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>051-724-7396</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-18</t>
+          <t>부산광역시 기장군 기장읍 차성로288번길 40</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1IMEHUc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5362,22 +5358,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,17 +5382,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1996364380</t>
+          <t>1494717985</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996364380</t>
+          <t>https://m.place.naver.com/place/1494717985</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5408,25 +5404,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>정숙한야시</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>h7292uj@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>051-724-8232</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로441번길 7</t>
+          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/h7292uj</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5476,17 +5476,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1074484941</t>
+          <t>16855482</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074484941</t>
+          <t>https://m.place.naver.com/place/16855482</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5498,29 +5498,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>하루빛네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dbswndud9404@naver.com</t>
+          <t>baeyeonjo1@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1330-4762</t>
+          <t>0507-1407-7874</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로322번길 36 1층 영네</t>
+          <t>부산광역시 기장군 일광읍 해빛5로 26 이지더원2차 상가동 109호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dbswndud9404</t>
+          <t>https://www.instagram.com/daylight_nail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5570,17 +5570,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1527027904</t>
+          <t>1054374644</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527027904</t>
+          <t>https://m.place.naver.com/place/1054374644</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5592,34 +5592,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>더심플</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>soyaa814@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1404-8512</t>
+          <t>0507-1376-6218</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 이지더원3차아파트 323동 2층 113호 더심플</t>
+          <t>부산광역시 기장군 정관읍 모전로 79 1층 102호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.simple_nail?igsh=eHo2enB6MGZjNWQ0</t>
+          <t>https://open.kakao.com/o/s4fI6Dug</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5640,7 +5640,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5664,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1926904977</t>
+          <t>2026985488</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926904977</t>
+          <t>https://m.place.naver.com/place/2026985488</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5686,34 +5686,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>이안네일</t>
+          <t>써니네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wendyandj@naver.com</t>
+          <t>sunnynails_busan@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1307-2082</t>
+          <t>0507-1347-9633</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로142번길 11 골든그린빌상가 B동 1층</t>
+          <t>부산광역시 기장군 기장읍 차성동로45번길 1 동부산렉슬 204호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/iann_nail</t>
+          <t>https://www.youtube.com/@Sunny_Nails</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="R57" t="n">
-        <v>9</v>
+        <v>157</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,17 +5758,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1275481649</t>
+          <t>1732198376</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275481649</t>
+          <t>https://m.place.naver.com/place/1732198376</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5780,25 +5780,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>비니네일</t>
+          <t>엔포유온네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>eternel__01@naver.com</t>
+          <t>paster33@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1352-1221</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 차성동로 92 LG장식</t>
+          <t>부산광역시 기장군 일광읍 해빛4로 1 B층 117호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/n4u.on_nail</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5808,7 +5812,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5829,17 +5833,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,17 +5852,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1734190871</t>
+          <t>2086668706</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1734190871</t>
+          <t>https://m.place.naver.com/place/2086668706</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5870,39 +5874,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일봉봉</t>
+          <t>네일, 살랑</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ye0505@naver.com</t>
+          <t>blackholecd@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1310-0650</t>
+          <t>0507-1347-5811</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 대청로45번길 19 103호</t>
+          <t>부산광역시 기장군 정관읍 가동3로 54-4 1층 네일, 살랑</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_XxfxfxoK</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5918,22 +5922,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,17 +5946,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1569463367</t>
+          <t>1311109904</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569463367</t>
+          <t>https://m.place.naver.com/place/1311109904</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5964,29 +5968,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>리아드네일</t>
+          <t>H에스테틱</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wpwlgus0219@naver.com</t>
+          <t>syuri__@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1304-6134</t>
+          <t>0507-1406-3277</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 430 2층 208호</t>
+          <t>부산광역시 기장군 기장읍 차성동로182번길 9</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_y.liad_nail</t>
+          <t>https://www.instagram.com/nailby_h</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6021,13 +6025,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="Q60" t="n">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="R60" t="n">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +6040,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1202615718</t>
+          <t>1758643778</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202615718</t>
+          <t>https://m.place.naver.com/place/1758643778</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6058,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일비</t>
+          <t>에반뷰티</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>panic9861@naver.com</t>
+          <t>evan_b9@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1428-4178</t>
+          <t>0507-1342-7372</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로87번길 28 1층</t>
+          <t>부산광역시 기장군 기장읍 차성로390번길 15 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bs_nailbee?igsh=dnI4a2s5ZzJpMW10</t>
+          <t>https://www.instagram.com/evan_beauty_/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6115,13 +6119,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>60</v>
+        <v>287</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="R61" t="n">
-        <v>62</v>
+        <v>430</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,17 +6134,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2039408171</t>
+          <t>1626526500</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039408171</t>
+          <t>https://m.place.naver.com/place/1626526500</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6152,29 +6156,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>네일앤아이래쉬</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>naileyelashes@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>051-728-3804</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관7로 3</t>
+          <t>부산광역시 기장군 정관읍 정관1로 18 126동 103호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/naileyelashes</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6224,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>32434749</t>
+          <t>1000195214</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32434749</t>
+          <t>https://m.place.naver.com/place/1000195214</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6246,29 +6246,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>도토리네일</t>
+          <t>네일코코</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>hydestocker@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1325-6971</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전3길 31 1층</t>
+          <t>부산광역시 기장군 정관읍 정관로 501-21 1층 102호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/do.tori_nail</t>
+          <t>http://instagram.com/nail_coco__jju</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6303,13 +6299,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,17 +6314,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2083351756</t>
+          <t>1109274522</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2083351756</t>
+          <t>https://m.place.naver.com/place/1109274522</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6340,39 +6336,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>님프네일</t>
+          <t>네일 프롬유</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>bojeong2626@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1439-0148</t>
+          <t>0507-1307-0453</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로55번길 6 1층 님프네일</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안 전통상가 1층 A137호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/from____you/?igshid=YmMyMTA2M2Y%3D</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6397,13 +6393,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R64" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6408,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1168958292</t>
+          <t>1603411217</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168958292</t>
+          <t>https://m.place.naver.com/place/1603411217</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6430,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>727nail</t>
+          <t>님프네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6443,26 +6439,30 @@
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1439-0148</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 324동 108호</t>
+          <t>부산광역시 기장군 기장읍 차성남로55번길 6 1층 님프네일</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/727nail</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6502,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2018352334</t>
+          <t>1168958292</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018352334</t>
+          <t>https://m.place.naver.com/place/1168958292</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6524,29 +6524,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일샵끌리다</t>
+          <t>모해, 네일앤뷰티</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mame0508@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1342-9503</t>
+          <t>051-727-0080</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛2로 24 비스타동원1차상가 128호</t>
+          <t>부산광역시 기장군 정관읍 정관로 581 성원프라자 116호 모해, 네일앤뷰티</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mame0508</t>
+          <t>https://www.instagram.com/sukyung_nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6581,13 +6581,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6596,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1462469485</t>
+          <t>30839584</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462469485</t>
+          <t>https://m.place.naver.com/place/30839584</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6618,34 +6618,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일빛</t>
+          <t>네일은빛나게</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kimmihee4@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1415-3379</t>
+          <t>0507-1303-4148</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 45 101호 네일빛</t>
+          <t>부산광역시 기장군 정관읍 모전1길 74 102호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bit.kr</t>
+          <t>https://pf.kakao.com/_PtVxcxb/chat</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6666,7 +6666,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>89</v>
+        <v>279</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6690,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1283671318</t>
+          <t>1538578837</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283671318</t>
+          <t>https://m.place.naver.com/place/1538578837</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6712,29 +6712,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>디오네일뷰티스튜디오</t>
+          <t>몽비쥬네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jjin0723@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1412-2457</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관1로 18 이지 더원1차 아파트 상가 125동 B105호</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_o_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6744,7 +6740,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6760,22 +6756,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,17 +6780,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1250273367</t>
+          <t>1882702996</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250273367</t>
+          <t>https://m.place.naver.com/place/1882702996</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6806,29 +6802,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>하루빛네일</t>
+          <t>네일빛</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>baeyeonjo1@naver.com</t>
+          <t>eunbi0888@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1407-7874</t>
+          <t>0507-1415-3379</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛5로 26 이지더원2차 상가동 109호</t>
+          <t>부산광역시 기장군 일광읍 해빛로 45 101호 네일빛</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daylight_nail</t>
+          <t>https://www.instagram.com/nail_bit.kr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6863,13 +6859,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6878,17 +6874,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1054374644</t>
+          <t>1283671318</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054374644</t>
+          <t>https://m.place.naver.com/place/1283671318</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6900,33 +6896,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>봄봄</t>
+          <t>빅토리네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>bbpub@naver.com</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>ir@daangn.com</t>
-        </is>
-      </c>
+          <t>kko-maeng@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1365-7606</t>
+          <t>0507-1330-2859</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 11 104호 봄봄</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 B112호(미래안 전통상가)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.daangn.com/kr/business-profiles/봄봄-23abca3f38a74635bf31eb721f6afc92</t>
+          <t>https://open.kakao.com/o/sUIlR3Qe</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6952,7 +6944,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6961,13 +6953,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,17 +6968,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1754904846</t>
+          <t>1968808024</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754904846</t>
+          <t>https://m.place.naver.com/place/1968808024</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6998,25 +6990,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일코코</t>
+          <t>그녀, 빛나네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>hydestocker@naver.com</t>
+          <t>usdbaoh24@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1352-6632</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 501-21 1층 102호</t>
+          <t>부산광역시 기장군 정관읍 정관5로 12 상가226동 103호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_coco__jju</t>
+          <t>https://www.instagram.com/shesshining_nail?igsh=bDQ4eDh2cjZp</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7051,13 +7047,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,17 +7062,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1109274522</t>
+          <t>1874020835</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109274522</t>
+          <t>https://m.place.naver.com/place/1874020835</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7088,25 +7084,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>임네일</t>
+          <t>정관소노네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hj_zzang@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1390-5016</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 563 건물(광장메디컬)</t>
+          <t>부산광역시 기장군 정관읍 달산2길 25-3 로얄하우스 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/im_nail_shin</t>
+          <t>https://www.instagram.com/sono_b.t</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="Q72" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7156,17 +7156,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1205209921</t>
+          <t>1535038585</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205209921</t>
+          <t>https://m.place.naver.com/place/1535038585</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7178,25 +7178,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>손톱</t>
+          <t>디오네일뷰티스튜디오</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gertrude01@naver.com</t>
+          <t>jjin0723@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1412-2457</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡3로 11 서희 스타힐스 상가동 102호</t>
+          <t>부산광역시 기장군 정관읍 정관1로 18 이지 더원1차 아파트 상가 125동 B105호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://instagram.com/sontob_nail</t>
+          <t>https://www.instagram.com/d_o_beauty</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7222,7 +7226,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7231,13 +7235,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R73" t="n">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7246,17 +7250,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>387880231</t>
+          <t>1250273367</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/387880231</t>
+          <t>https://m.place.naver.com/place/1250273367</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7268,29 +7272,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일은맑음</t>
+          <t>제이밈네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kkje38317@naver.com</t>
+          <t>jaeny__@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1412-1149</t>
+          <t>0507-1472-4423</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛6로 55 1층 네일은맑음</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 122 103호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/j_mim_nail?igsh=bXdqZmVmcmxwNWcy</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7316,22 +7320,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7340,17 +7344,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2017375277</t>
+          <t>1582950449</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017375277</t>
+          <t>https://m.place.naver.com/place/1582950449</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7362,24 +7366,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>보니네일&amp;좌훈카페</t>
+          <t>네일은맑음</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>kkje38317@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>051-727-1632</t>
+          <t>0507-1412-1149</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관중앙로 58</t>
+          <t>부산광역시 기장군 일광읍 해빛6로 55 1층 네일은맑음</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7422,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7434,17 +7438,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>34624678</t>
+          <t>2017375277</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34624678</t>
+          <t>https://m.place.naver.com/place/2017375277</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7456,39 +7460,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>비니네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>eternel__01@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1371-2638</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전3길 43 102호</t>
+          <t>부산광역시 기장군 차성동로 92 LG장식</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkXxcqX/friend</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7504,22 +7504,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7528,17 +7528,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2043055430</t>
+          <t>1734190871</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043055430</t>
+          <t>https://m.place.naver.com/place/1734190871</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>제이오스카네일 기장일광점</t>
+          <t>아이엠네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>joscar_nail@naver.com</t>
+          <t>gofhd1215@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1406-5802</t>
+          <t>0507-1398-5369</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 43 제이오스카 네일</t>
+          <t>부산광역시 기장군 정관읍 달산길 11 . 101호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.oscar_nail</t>
+          <t>https://www.instagram.com/lm_nail_90</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7607,13 +7607,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R77" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7622,17 +7622,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1177930986</t>
+          <t>1098146719</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177930986</t>
+          <t>https://m.place.naver.com/place/1098146719</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7644,34 +7644,34 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>코델리아진네일뷰티</t>
+          <t>빛나담 뷰티테라스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>bitnadal_bt@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1316-8137</t>
+          <t>0507-1388-6656</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 기장해안로 98 C211호</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 72 4층 401호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sbFNXENb</t>
+          <t>https://www.instagram.com/bitnadam_bt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7692,7 +7692,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7701,13 +7701,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>284</v>
       </c>
       <c r="Q78" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="R78" t="n">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7716,17 +7716,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1451145377</t>
+          <t>1729711839</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451145377</t>
+          <t>https://m.place.naver.com/place/1729711839</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7738,34 +7738,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>빅토리네일</t>
+          <t>뷰티샤네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kko-maeng@naver.com</t>
+          <t>daumi0820@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1330-2859</t>
+          <t>0507-1354-4413</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 B112호(미래안 전통상가)</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 213동 b201호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUIlR3Qe</t>
+          <t>https://www.instagram.com/beautychanail</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7786,7 +7786,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7795,13 +7795,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="Q79" t="n">
         <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7810,17 +7810,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1968808024</t>
+          <t>1573379404</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968808024</t>
+          <t>https://m.place.naver.com/place/1573379404</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7832,25 +7832,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>누아네일</t>
+          <t>연하뷰티네일</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>cjfng@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1464-4702</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 9 102동 B103층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-8 5층 502호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nua_lashperm?igsh=N2xlN2JsMnBjNnQw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7860,7 +7864,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7881,17 +7885,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q80" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7900,17 +7904,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2022687189</t>
+          <t>2067837278</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022687189</t>
+          <t>https://m.place.naver.com/place/2067837278</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7922,29 +7926,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>아이엠네일</t>
+          <t>네일리쥬</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>gofhd1215@naver.com</t>
+          <t>dbdud0328@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1398-5369</t>
+          <t>0507-1384-0540</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산길 11 . 101호</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 213동 B206호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lm_nail_90</t>
+          <t>https://www.instagram.com/nail_leeju</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7970,7 +7974,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7979,13 +7983,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R81" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7994,17 +7998,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1098146719</t>
+          <t>1360272320</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098146719</t>
+          <t>https://m.place.naver.com/place/1360272320</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8016,39 +8020,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>어니st네일</t>
+          <t>네일더무드 부산정관점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>audwn082@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1419-2720</t>
+          <t>0507-1434-9030</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 122 디바인스퀘어 상가 1층</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 상가 B209호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_UxdxlxlG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8064,22 +8068,22 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="Q82" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8088,17 +8092,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1544355473</t>
+          <t>1467606881</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544355473</t>
+          <t>https://m.place.naver.com/place/1467606881</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8110,29 +8114,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일더무드 부산정관점</t>
+          <t>보니따뷰티</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>gjbarun@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1434-9030</t>
+          <t>051-722-7004</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 상가 B209호</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/bonitabeauty_bb</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8142,7 +8146,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8163,17 +8167,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>140</v>
+        <v>437</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>142</v>
+        <v>442</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8182,17 +8186,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1467606881</t>
+          <t>1059332253</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467606881</t>
+          <t>https://m.place.naver.com/place/1059332253</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8204,24 +8208,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>즐거운네일</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>luv0e@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1433-3022</t>
+          <t>0507-1362-5752</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관덕산길 80 파스텔라상가 1층 6호 즐거운네일</t>
+          <t>부산광역시 기장군 정관읍 가동2길 24-7 리네일</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8261,13 +8265,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>560</v>
+        <v>5</v>
       </c>
       <c r="Q84" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>573</v>
+        <v>6</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8276,17 +8280,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1490033165</t>
+          <t>1105532713</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490033165</t>
+          <t>https://m.place.naver.com/place/1105532713</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8298,29 +8302,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일 프롬유</t>
+          <t>즐거운네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>bojeong2626@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1307-0453</t>
+          <t>0507-1433-3022</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안 전통상가 1층 A137호</t>
+          <t>부산광역시 기장군 정관읍 정관덕산길 80 파스텔라상가 1층 6호 즐거운네일</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/from____you/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8330,7 +8334,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8351,17 +8355,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>96</v>
+        <v>563</v>
       </c>
       <c r="Q85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R85" t="n">
-        <v>107</v>
+        <v>576</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8370,17 +8374,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1603411217</t>
+          <t>1490033165</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1603411217</t>
+          <t>https://m.place.naver.com/place/1490033165</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8396,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>몽비쥬네일</t>
+          <t>보니네일&amp;좌훈카페</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8401,11 +8405,15 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>051-727-1632</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
+          <t>부산광역시 기장군 정관읍 정관중앙로 58</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8460,17 +8468,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1882702996</t>
+          <t>34624678</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882702996</t>
+          <t>https://m.place.naver.com/place/34624678</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8482,12 +8490,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>정관노바네일</t>
+          <t>마이네일숍</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>angel9708@naver.com</t>
+          <t>hanzzang25@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8495,12 +8503,12 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층</t>
+          <t>부산광역시 기장군 장안읍 길천길 15 1층 101호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nova__beauty__</t>
+          <t>https://www.instagram.com/mynailshop_</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8535,13 +8543,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>929</v>
+        <v>3</v>
       </c>
       <c r="Q87" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>954</v>
+        <v>4</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8550,17 +8558,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1011332772</t>
+          <t>1576268118</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011332772</t>
+          <t>https://m.place.naver.com/place/1576268118</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8572,29 +8580,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>김동주네일미학</t>
+          <t>리나운 뷰티가든</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>muggle4@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>051-722-3773</t>
+          <t>0507-1442-7669</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 11</t>
+          <t>부산광역시 기장군 기장읍 차성로344번길 13 상가동 114호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/renown_nail7667?igsh=MXhuaDBvYzJ4N3lhZQ==</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8604,7 +8612,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8625,17 +8633,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8644,17 +8652,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>12939947</t>
+          <t>1230254733</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12939947</t>
+          <t>https://m.place.naver.com/place/1230254733</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8666,29 +8674,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>정관 민뷰티크</t>
+          <t>김동주네일미학</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>muggle4@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1357-3978</t>
+          <t>051-722-3773</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 545 홈플러스 정문 바로맞은편 길가</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 11</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/min._.boutique</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8698,7 +8706,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8719,17 +8727,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8738,17 +8746,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1517396176</t>
+          <t>12939947</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517396176</t>
+          <t>https://m.place.naver.com/place/12939947</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8760,34 +8768,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>써니네일</t>
+          <t>임네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sunnynails_busan@naver.com</t>
+          <t>hj_zzang@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1347-9633</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로45번길 1 동부산렉슬 204호</t>
+          <t>부산광역시 기장군 정관읍 정관로 563 건물(광장메디컬)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Sunny_Nails</t>
+          <t>https://www.instagram.com/im_nail_shin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8817,13 +8821,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="Q90" t="n">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="R90" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8832,17 +8836,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1732198376</t>
+          <t>1205209921</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732198376</t>
+          <t>https://m.place.naver.com/place/1205209921</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8854,24 +8858,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>르포렘네일</t>
+          <t>수진네일아트</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>tngus3985@naver.com</t>
+          <t>linnii@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1496-3223</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동길 13-10 102호</t>
+          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8911,13 +8911,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="Q91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8926,17 +8926,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1097788106</t>
+          <t>1769136676</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097788106</t>
+          <t>https://m.place.naver.com/place/1769136676</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8948,29 +8948,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>보니따뷰티</t>
+          <t>네일,은</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gjbarun@naver.com</t>
+          <t>minukyung@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>051-722-7004</t>
+          <t>0507-1373-0854</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 5</t>
+          <t>부산광역시 기장군 정관읍 정관로 383 대성타워빌딩 B103호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>http://instagram.com/bonitabeauty_bb</t>
+          <t>https://www.instagram.com/_nail.eun_/profilecard/?igsh=MXhid2VxMzVrdmMwYQ==</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9020,17 +9020,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1059332253</t>
+          <t>1799936115</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059332253</t>
+          <t>https://m.place.naver.com/place/1799936115</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9042,44 +9042,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>은네일에스테틱</t>
+          <t>네일밍</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>ksk98815@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1368-7222</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 읍내로 122 2층 은네일&amp;에스테틱</t>
+          <t>부산광역시 기장군 정관읍 모전1길 72 . 1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ming1226</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9095,17 +9091,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9114,17 +9110,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1386160942</t>
+          <t>1326191176</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386160942</t>
+          <t>https://m.place.naver.com/place/1326191176</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9136,34 +9132,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>더네일킹</t>
+          <t>정관마일리네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ovoa333@naver.com</t>
+          <t>tinda_com@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1391-3331</t>
+          <t>0507-1361-4832</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동1길 11-5 1층</t>
+          <t>부산광역시 기장군 정관읍 정관로 579 6층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_nailking</t>
+          <t>http://pf.kakao.com/_iGXxgC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9184,7 +9180,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9193,13 +9189,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>143</v>
+        <v>1176</v>
       </c>
       <c r="Q94" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R94" t="n">
-        <v>146</v>
+        <v>1201</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9208,17 +9204,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1661274406</t>
+          <t>1181950337</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661274406</t>
+          <t>https://m.place.naver.com/place/1181950337</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9230,25 +9226,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>바비네일</t>
+          <t>제이오스카네일 기장일광점</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>zasd43@naver.com</t>
+          <t>joscar_nail@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1406-5802</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 43 제이오스카 네일</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/j.oscar_nail</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9279,17 +9279,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="R95" t="n">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,17 +9298,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1133605184</t>
+          <t>1177930986</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1133605184</t>
+          <t>https://m.place.naver.com/place/1177930986</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9320,25 +9320,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>어게인뷰티</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>daliboni@naver.com</t>
+          <t>dbswndud9404@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1330-4762</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전로 78-1 1층 101호</t>
+          <t>부산광역시 기장군 기장읍 차성로322번길 36 1층 영네</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/again_b.t</t>
+          <t>https://blog.naver.com/dbswndud9404</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9353,7 +9357,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9373,13 +9377,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q96" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9388,17 +9392,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1843319378</t>
+          <t>1527027904</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843319378</t>
+          <t>https://m.place.naver.com/place/1527027904</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9410,34 +9414,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>어게인뷰티</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jytgh@naver.com</t>
+          <t>daliboni@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>051-722-1551</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛5로 21-3 지음프라자 2층</t>
+          <t>부산광역시 기장군 정관읍 모전로 78-1 1층 101호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nabi.nail_</t>
+          <t>https://www.instagram.com/again_b.t</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9467,13 +9467,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9482,17 +9482,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>20557575</t>
+          <t>1843319378</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20557575</t>
+          <t>https://m.place.naver.com/place/1843319378</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9598,29 +9598,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>네일은빛나게</t>
+          <t>어니st네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>audwn082@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1303-4148</t>
+          <t>0507-1419-2720</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 74 102호</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 122 디바인스퀘어 상가 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_PtVxcxb/chat</t>
+          <t>https://pf.kakao.com/_UxdxlxlG</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="Q99" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R99" t="n">
-        <v>281</v>
+        <v>186</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9670,47 +9670,51 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1538578837</t>
+          <t>1544355473</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538578837</t>
+          <t>https://m.place.naver.com/place/1544355473</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>임대업</t>
+          <t>속눈썹증모,연장</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>듀얼모멘텀</t>
+          <t>이지뷰티샵</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ljhh4202@naver.com</t>
+          <t>tamtamiii@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1392-0479</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관덕산길 41 동우오피스텔 201호</t>
+          <t>부산광역시 기장군 정관읍 정관중앙로 45 4층 407호 이지뷰티샵</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/eg_beauty_brow?igsh=M2c2ZWpnMzR0ejY%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9720,7 +9724,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9741,36 +9745,126 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>9</v>
+      </c>
+      <c r="R100" t="n">
+        <v>64</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1996184739</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1996184739</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>임대업</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>듀얼모멘텀</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>youreit@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>부산광역시 기장군 정관읍 정관덕산길 41 동우오피스텔 201호</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q101" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
         <is>
           <t>1706241878</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1706241878</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/기장군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/기장군_네일샵.xlsx
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>정관 민뷰티크</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>즐거운네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1357-3978</t>
+          <t>0507-1433-3022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 545 홈플러스 정문 바로맞은편 길가</t>
+          <t>부산광역시 기장군 정관읍 정관덕산길 80 파스텔라상가 1층 6호 즐거운네일</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/min._.boutique</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>36</v>
+        <v>566</v>
       </c>
       <c r="Q2" t="n">
         <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>49</v>
+        <v>579</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1517396176</t>
+          <t>1490033165</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517396176</t>
+          <t>https://m.place.naver.com/place/1490033165</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정관 아린네일</t>
+          <t>빛나담 뷰티테라스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lla0020@naver.com</t>
+          <t>bitnadal_bt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-727-1544</t>
+          <t>0507-1388-6656</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 485 롯데캐슬프라자</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 72 4층 401호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bitnadam_bt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>380</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1312537670</t>
+          <t>1729711839</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312537670</t>
+          <t>https://m.place.naver.com/place/1729711839</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,7 +748,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코델리아진네일뷰티</t>
+          <t>남자다운네일 본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -763,28 +759,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1316-8137</t>
+          <t>051-724-7396</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 기장해안로 98 C211호</t>
+          <t>부산광역시 기장군 기장읍 차성로288번길 40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sbFNXENb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -800,22 +796,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1451145377</t>
+          <t>1494717985</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451145377</t>
+          <t>https://m.place.naver.com/place/1494717985</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일스케치</t>
+          <t>정관네일하러가</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kongdw@naver.com</t>
+          <t>nailharuga@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>051-724-3373</t>
+          <t>0507-1325-6461</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로 73</t>
+          <t>부산광역시 기장군 정관읍 가동3로 24 서언빈 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailharuga</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +874,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>415</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>426</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31517196</t>
+          <t>1972636570</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31517196</t>
+          <t>https://m.place.naver.com/place/1972636570</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빈s magic</t>
+          <t>네일,은</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>overcome6@naver.com</t>
+          <t>minukyung@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1359-6914</t>
+          <t>0507-1373-0854</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로 63 1층 빈s magic</t>
+          <t>부산광역시 기장군 정관읍 정관로 383 대성타워빌딩 B103호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nail.eun_/profilecard/?igsh=MXhid2VxMzVrdmMwYQ==</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1527971991</t>
+          <t>1799936115</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527971991</t>
+          <t>https://m.place.naver.com/place/1799936115</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,30 +1030,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일,만나</t>
+          <t>정관소노네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ehgptn321@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1390-5016</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-18</t>
+          <t>부산광역시 기장군 정관읍 달산2길 25-3 로얄하우스 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1IMEHUc</t>
+          <t>https://www.instagram.com/sono_b.t</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1996364380</t>
+          <t>1535038585</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996364380</t>
+          <t>https://m.place.naver.com/place/1535038585</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1124,25 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>727nail</t>
+          <t>그녀, 빛나네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>usdbaoh24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1352-6632</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 324동 108호</t>
+          <t>부산광역시 기장군 정관읍 정관5로 12 상가226동 103호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/727nail</t>
+          <t>https://www.instagram.com/shesshining_nail?igsh=bDQ4eDh2cjZp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2018352334</t>
+          <t>1874020835</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018352334</t>
+          <t>https://m.place.naver.com/place/1874020835</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,40 +1218,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일스토리</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yeju0414@naver.com</t>
-        </is>
-      </c>
+          <t>네일스케치</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>051-724-3373</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 2 1층</t>
+          <t>부산광역시 기장군 기장읍 차성동로 73</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CSrI-pVFHtQ/?utm_medium=copy_link</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1263,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1586444618</t>
+          <t>31517196</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1586444618</t>
+          <t>https://m.place.naver.com/place/31517196</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1304,25 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일향</t>
+          <t>정관 민뷰티크</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>joen1204@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1357-3978</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로65번길 11</t>
+          <t>부산광역시 기장군 정관읍 정관로 545 홈플러스 정문 바로맞은편 길가</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/min._.boutique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1332,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1353,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>19693133</t>
+          <t>1517396176</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19693133</t>
+          <t>https://m.place.naver.com/place/1517396176</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1394,25 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>누아네일</t>
+          <t>리아드네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cjfng@naver.com</t>
+          <t>wpwlgus0219@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1304-6134</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 9 102동 B103층</t>
+          <t>부산광역시 기장군 기장읍 차성로 430 2층 208호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nua_lashperm?igsh=N2xlN2JsMnBjNnQw</t>
+          <t>https://www.instagram.com/_y.liad_nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="R11" t="n">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2022687189</t>
+          <t>1202615718</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022687189</t>
+          <t>https://m.place.naver.com/place/1202615718</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1484,29 +1496,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jytgh@naver.com</t>
-        </is>
-      </c>
+          <t>이안네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>051-722-1551</t>
+          <t>0507-1307-2082</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛5로 21-3 지음프라자 2층</t>
+          <t>부산광역시 기장군 기장읍 차성동로142번길 11 골든그린빌상가 B동 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nabi.nail_</t>
+          <t>http://www.instagram.com/iann_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>20557575</t>
+          <t>1275481649</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20557575</t>
+          <t>https://m.place.naver.com/place/1275481649</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1578,34 +1586,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>더네일킹</t>
+          <t>봄봄</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ovoa333@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>bbpub@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ir@daangn.com</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1391-3331</t>
+          <t>0507-1365-7606</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동1길 11-5 1층</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 11 104호 봄봄</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_nailking</t>
+          <t>https://www.daangn.com/kr/business-profiles/봄봄-23abca3f38a74635bf31eb721f6afc92</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1635,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1661274406</t>
+          <t>1754904846</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661274406</t>
+          <t>https://m.place.naver.com/place/1754904846</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1672,25 +1684,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>여우숲네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hanna7342@naver.com</t>
-        </is>
-      </c>
+          <t>하루빛네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1407-7874</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로332번길 14 여우숲 네일</t>
+          <t>부산광역시 기장군 일광읍 해빛5로 26 이지더원2차 상가동 109호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://instagram.com/lovely_lail_6604</t>
+          <t>https://www.instagram.com/daylight_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1725,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1740,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1249638908</t>
+          <t>1054374644</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249638908</t>
+          <t>https://m.place.naver.com/place/1054374644</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1762,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코델리아네일뷰티</t>
+          <t>에반뷰티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>evan_b9@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1336-8137</t>
+          <t>0507-1342-7372</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 41 아이프라자 1차 603호</t>
+          <t>부산광역시 기장군 기장읍 차성로390번길 15 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_codellia.jin</t>
+          <t>https://www.instagram.com/evan_beauty_/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>44</v>
+        <v>287</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="R15" t="n">
-        <v>53</v>
+        <v>430</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1834,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1736623275</t>
+          <t>1626526500</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1736623275</t>
+          <t>https://m.place.naver.com/place/1626526500</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1856,34 +1868,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>베스타네일</t>
+          <t>네일코코</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>hydestocker@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1398-1666</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송4로 21 일광프라자 3층 304호</t>
+          <t>부산광역시 기장군 정관읍 정관로 501-21 1층 102호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/me/vesta</t>
+          <t>http://instagram.com/nail_coco__jju</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1904,7 +1912,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1913,13 +1921,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1936,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1527088754</t>
+          <t>1109274522</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527088754</t>
+          <t>https://m.place.naver.com/place/1109274522</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1950,20 +1958,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>바비네일</t>
+          <t>네일경</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>zasd43@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1392-1745</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 322동103호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2003,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2018,17 +2030,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1133605184</t>
+          <t>1047568389</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1133605184</t>
+          <t>https://m.place.naver.com/place/1047568389</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2040,29 +2052,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더심플</t>
+          <t>코델리아네일뷰티</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>soyaa814@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1404-8512</t>
+          <t>0507-1336-8137</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 이지더원3차아파트 323동 2층 113호 더심플</t>
+          <t>부산광역시 기장군 일광읍 해빛로 41 아이프라자 1차 603호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.simple_nail?igsh=eHo2enB6MGZjNWQ0</t>
+          <t>https://www.instagram.com/beauty_codellia.jin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,13 +2109,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2112,17 +2124,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1926904977</t>
+          <t>1736623275</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926904977</t>
+          <t>https://m.place.naver.com/place/1736623275</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2146,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일홀릭</t>
+          <t>네일샵끌리다</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>minmin0319@naver.com</t>
+          <t>mame0508@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1362-0848</t>
+          <t>0507-1342-9503</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산길 22-11 1층 네일홀릭</t>
+          <t>부산광역시 기장군 일광읍 해빛2로 24 비스타동원1차상가 128호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mame0508</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2166,12 +2178,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2187,17 +2199,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2206,17 +2218,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1461860750</t>
+          <t>1462469485</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461860750</t>
+          <t>https://m.place.naver.com/place/1462469485</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2228,29 +2240,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>이지민네일</t>
+          <t>누아네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>cjfng@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1364-4182</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안전통상가 108-2호</t>
+          <t>부산광역시 기장군 정관읍 모전1길 9 102동 B103층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/wings_0331</t>
+          <t>https://www.instagram.com/nua_lashperm?igsh=N2xlN2JsMnBjNnQw</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,13 +2293,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,17 +2308,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1955852559</t>
+          <t>2022687189</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955852559</t>
+          <t>https://m.place.naver.com/place/2022687189</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2322,29 +2330,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일샵끌리다</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>mame0508@naver.com</t>
-        </is>
-      </c>
+          <t>은네일에스테틱</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1342-9503</t>
+          <t>0507-1368-7222</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛2로 24 비스타동원1차상가 128호</t>
+          <t>부산광역시 기장군 기장읍 읍내로 122 2층 은네일&amp;에스테틱</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mame0508</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2375,17 +2379,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2394,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1462469485</t>
+          <t>1386160942</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462469485</t>
+          <t>https://m.place.naver.com/place/1386160942</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2416,34 +2420,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>어썸네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>loves0226@naver.com</t>
-        </is>
-      </c>
+          <t>정관노바네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1371-2638</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전3길 43 102호</t>
+          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkXxcqX/friend</t>
+          <t>http://www.instagram.com/nova__beauty__</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2464,7 +2460,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2473,13 +2469,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>112</v>
+        <v>931</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R22" t="n">
-        <v>141</v>
+        <v>956</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2488,17 +2484,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2043055430</t>
+          <t>1011332772</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043055430</t>
+          <t>https://m.place.naver.com/place/1011332772</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2510,29 +2506,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일비</t>
+          <t>아모이네</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>panic9861@naver.com</t>
+          <t>moo_oong@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1428-4178</t>
+          <t>0507-1496-2088</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로87번길 28 1층</t>
+          <t>부산광역시 기장군 정관읍 정관5로 26 센텀프라자 1층 114호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bs_nailbee?igsh=dnI4a2s5ZzJpMW10</t>
+          <t>https://www.instagram.com/_amoene_</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2567,13 +2563,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2578,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2039408171</t>
+          <t>1587841336</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039408171</t>
+          <t>https://m.place.naver.com/place/1587841336</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2604,29 +2600,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>은네일에스테틱</t>
+          <t>마이네일숍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>hanzzang25@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1368-7222</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 읍내로 122 2층 은네일&amp;에스테틱</t>
+          <t>부산광역시 기장군 장안읍 길천길 15 1층 101호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mynailshop_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2636,7 +2628,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2657,17 +2649,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2668,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1386160942</t>
+          <t>1576268118</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386160942</t>
+          <t>https://m.place.naver.com/place/1576268118</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2698,34 +2690,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손끄치스치다</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>innazzang-@naver.com</t>
-        </is>
-      </c>
+          <t>네일, 살랑</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1432-1235</t>
+          <t>0507-1347-5811</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 . 323동 107호</t>
+          <t>부산광역시 기장군 정관읍 가동3로 54-4 1층 네일, 살랑</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0701_a_reum/</t>
+          <t>http://pf.kakao.com/_XxfxfxoK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2746,7 +2734,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2755,13 +2743,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2758,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>38479059</t>
+          <t>1311109904</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38479059</t>
+          <t>https://m.place.naver.com/place/1311109904</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,25 +2780,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일J</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>qpqptkfkd7@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1362-5752</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 305 1층 네일J</t>
+          <t>부산광역시 기장군 정관읍 가동2길 24-7 리네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qpqptkfkd7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2820,12 +2812,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2841,18 +2833,18 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
         <v>6</v>
       </c>
-      <c r="R26" t="n">
-        <v>10</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2860,17 +2852,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1688859881</t>
+          <t>1105532713</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688859881</t>
+          <t>https://m.place.naver.com/place/1105532713</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2882,29 +2874,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>난달라</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>nandala_nail@naver.com</t>
-        </is>
-      </c>
+          <t>더심플</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1406-0410</t>
+          <t>0507-1404-8512</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 구연방곡로 120 가화만사성더테라스1차302동108호</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 이지더원3차아파트 323동 2층 113호 더심플</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nandala_nail.0130</t>
+          <t>https://www.instagram.com/the.simple_nail?igsh=eHo2enB6MGZjNWQ0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2939,13 +2927,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2942,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1874677609</t>
+          <t>1926904977</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874677609</t>
+          <t>https://m.place.naver.com/place/1926904977</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2976,34 +2964,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>에이치네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>remon103@naver.com</t>
-        </is>
-      </c>
+          <t>님프네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1308-6632</t>
+          <t>0507-1439-0148</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 구연방곡로 10 정문상가104호</t>
+          <t>부산광역시 기장군 기장읍 차성남로55번길 6 1층 님프네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3029,17 +3013,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3048,17 +3032,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1252239066</t>
+          <t>1168958292</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252239066</t>
+          <t>https://m.place.naver.com/place/1168958292</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3070,43 +3054,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>봄봄</t>
+          <t>네일더무드 부산정관점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bbpub@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ad@daangn.com</t>
-        </is>
-      </c>
+          <t>wldms99888@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1365-7606</t>
+          <t>0507-1434-9030</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 11 104호 봄봄</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 상가 B209호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.daangn.com/kr/business-profiles/봄봄-23abca3f38a74635bf31eb721f6afc92</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3127,17 +3107,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3126,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1754904846</t>
+          <t>1467606881</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754904846</t>
+          <t>https://m.place.naver.com/place/1467606881</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3168,34 +3148,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일세르</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>네일빛</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1373-5187</t>
+          <t>0507-1415-3379</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 산단4로 153-12 101호</t>
+          <t>부산광역시 기장군 일광읍 해빛로 45 101호 네일빛</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iaIZX/chat</t>
+          <t>https://www.instagram.com/nail_bit.kr</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3216,7 +3192,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3225,13 +3201,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3216,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2062927983</t>
+          <t>1283671318</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062927983</t>
+          <t>https://m.place.naver.com/place/1283671318</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,29 +3238,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>정관네일하러가</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nailharuga@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1325-6461</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동3로 24 서언빈 1층</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharuga</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3294,7 +3266,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3315,17 +3287,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>415</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>426</v>
+        <v>5</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1972636570</t>
+          <t>1133605184</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972636570</t>
+          <t>https://m.place.naver.com/place/1133605184</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3356,34 +3328,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아모이네</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>moo_oong@naver.com</t>
-        </is>
-      </c>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1496-2088</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관5로 26 센텀프라자 1층 114호</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 2 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_amoene_</t>
+          <t>https://www.instagram.com/p/CSrI-pVFHtQ/?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3393,7 +3357,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3413,13 +3377,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3392,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1587841336</t>
+          <t>1586444618</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587841336</t>
+          <t>https://m.place.naver.com/place/1586444618</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3450,29 +3414,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>숩네일</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>hyunjju1541@naver.com</t>
-        </is>
-      </c>
+          <t>르포렘네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1467-1273</t>
+          <t>0507-1496-3223</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 기장대로 495 1층 107호</t>
+          <t>부산광역시 기장군 정관읍 가동길 13-10 102호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_su.b_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3482,7 +3442,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3503,17 +3463,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3482,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1430742656</t>
+          <t>1097788106</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430742656</t>
+          <t>https://m.place.naver.com/place/1097788106</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3544,29 +3504,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>요니네일</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>yoni_nail@naver.com</t>
-        </is>
-      </c>
+          <t>엔포유온네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1373-7728</t>
+          <t>0507-1352-1221</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로441번길 7 상가동 104호</t>
+          <t>부산광역시 기장군 일광읍 해빛4로 1 B층 117호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/n4u.on_nail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3576,7 +3532,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3597,17 +3553,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3572,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1905392632</t>
+          <t>2086668706</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1905392632</t>
+          <t>https://m.place.naver.com/place/2086668706</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3638,39 +3594,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일경</t>
+          <t>네일더예쁨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>angpang8119@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1392-1745</t>
+          <t>0507-1319-8116</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 350 322동103호</t>
+          <t>부산광역시 기장군 기장읍 차성동로 160 2층 네일더예쁨</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://clip.naver.com/yee_peumnail</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3691,17 +3647,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="R35" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3666,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1047568389</t>
+          <t>1502532902</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1047568389</t>
+          <t>https://m.place.naver.com/place/1502532902</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3732,29 +3688,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>샐리 네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>toy2968@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>051-728-3804</t>
+          <t>0507-1383-5654</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관7로 3</t>
+          <t>부산광역시 기장군 정관읍 정관2로 40 정관신도시 현진에버빌 211호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_sally_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3764,7 +3720,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3785,17 +3741,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3760,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>32434749</t>
+          <t>1321337327</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32434749</t>
+          <t>https://m.place.naver.com/place/1321337327</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3826,25 +3782,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>정관노바네일</t>
+          <t>이지민네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>angel9708@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1364-4182</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안전통상가 108-2호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nova__beauty__</t>
+          <t>http://instagram.com/wings_0331</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3879,13 +3839,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>930</v>
+        <v>58</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>955</v>
+        <v>65</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3894,17 +3854,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1011332772</t>
+          <t>1955852559</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011332772</t>
+          <t>https://m.place.naver.com/place/1955852559</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3916,25 +3876,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BaRa네일샵</t>
+          <t>아이엠네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>gofhd1215@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1398-5369</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로288번길 22 1층 BaRa 네일샵</t>
+          <t>부산광역시 기장군 정관읍 달산길 11 . 101호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lm_nail_90</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,7 +3908,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3965,17 +3929,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3948,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1766863509</t>
+          <t>1098146719</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766863509</t>
+          <t>https://m.place.naver.com/place/1098146719</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4006,29 +3970,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>지유네일 기장일광점</t>
+          <t>수진네일아트</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>linnii@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1359-9732</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 이화로 7 2층</t>
+          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailjiyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4038,7 +3998,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4059,17 +4019,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4038,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1722948905</t>
+          <t>1769136676</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722948905</t>
+          <t>https://m.place.naver.com/place/1769136676</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4100,25 +4060,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>정숙한야시</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>숩네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1467-1273</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로441번길 7</t>
+          <t>부산광역시 기장군 기장읍 기장대로 495 1층 107호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_su.b_nail_</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4128,7 +4088,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4149,17 +4109,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4128,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1074484941</t>
+          <t>1430742656</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074484941</t>
+          <t>https://m.place.naver.com/place/1430742656</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4190,29 +4150,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>리아드네일</t>
+          <t>몽비쥬네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wpwlgus0219@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1304-6134</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 430 2층 208호</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_y.liad_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4222,7 +4178,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4243,17 +4199,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4218,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1202615718</t>
+          <t>1882702996</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202615718</t>
+          <t>https://m.place.naver.com/place/1882702996</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4284,29 +4240,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>검은고양이네일</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>mmins-0610@naver.com</t>
-        </is>
-      </c>
+          <t>도토리네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1320-6761</t>
+          <t>0507-1325-6971</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡로 29</t>
+          <t>부산광역시 기장군 정관읍 모전3길 31 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blackcat.mqpon.co.kr/</t>
+          <t>https://www.instagram.com/do.tori_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4337,17 +4289,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,17 +4308,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1921074769</t>
+          <t>2083351756</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1921074769</t>
+          <t>https://m.place.naver.com/place/2083351756</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4378,29 +4330,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일봉봉</t>
+          <t>써니네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ye0505@naver.com</t>
+          <t>sunnynails_busan@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1310-0650</t>
+          <t>0507-1347-9633</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 대청로45번길 19 103호</t>
+          <t>부산광역시 기장군 기장읍 차성동로45번길 1 동부산렉슬 204호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.youtube.com/@Sunny_Nails</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4410,7 +4362,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4431,17 +4383,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,17 +4402,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1569463367</t>
+          <t>1732198376</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569463367</t>
+          <t>https://m.place.naver.com/place/1732198376</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4472,25 +4424,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>손톱</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gertrude01@naver.com</t>
+          <t>jjuri272@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>051-722-1551</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡3로 11 서희 스타힐스 상가동 102호</t>
+          <t>부산광역시 기장군 일광읍 해빛5로 21-3 지음프라자 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/sontob_nail</t>
+          <t>https://www.instagram.com/nabi.nail_</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4525,13 +4481,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4540,17 +4496,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>387880231</t>
+          <t>20557575</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/387880231</t>
+          <t>https://m.place.naver.com/place/20557575</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4562,29 +4518,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>르포렘네일</t>
+          <t>제이밈네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jiuhhuj@naver.com</t>
+          <t>jaeny__@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1496-3223</t>
+          <t>0507-1472-4423</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동길 13-10 102호</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 122 103호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/j_mim_nail?igsh=bXdqZmVmcmxwNWcy</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4594,7 +4550,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4610,22 +4566,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4634,17 +4590,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1097788106</t>
+          <t>1582950449</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097788106</t>
+          <t>https://m.place.naver.com/place/1582950449</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4656,39 +4612,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일더예쁨</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>angpang8119@naver.com</t>
-        </is>
-      </c>
+          <t>신데렐라네일아트</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1319-8116</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로 160 2층 네일더예쁨</t>
+          <t>부산광역시 기장군 철마면 고촌로28번길 3</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://clip.naver.com/yee_peumnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4709,17 +4657,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4728,17 +4676,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1502532902</t>
+          <t>1842273793</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1502532902</t>
+          <t>https://m.place.naver.com/place/1842273793</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4750,34 +4698,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>샐리 네일</t>
+          <t>네일은빛나게</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>toy2968@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1383-5654</t>
+          <t>0507-1303-4148</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 40 정관신도시 현진에버빌 211호</t>
+          <t>부산광역시 기장군 정관읍 모전1길 74 102호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sally_nail</t>
+          <t>https://pf.kakao.com/_PtVxcxb/chat</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4798,7 +4746,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4807,13 +4755,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>169</v>
+        <v>281</v>
       </c>
       <c r="Q47" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="R47" t="n">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4770,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1321337327</t>
+          <t>1538578837</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1321337327</t>
+          <t>https://m.place.naver.com/place/1538578837</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4844,29 +4792,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>도토리네일</t>
+          <t>손톱</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>gertrude01@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1325-6971</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전3길 31 1층</t>
+          <t>부산광역시 기장군 정관읍 방곡3로 11 서희 스타힐스 상가동 102호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/do.tori_nail</t>
+          <t>http://instagram.com/sontob_nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4901,13 +4845,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4916,17 +4860,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2083351756</t>
+          <t>387880231</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2083351756</t>
+          <t>https://m.place.naver.com/place/387880231</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4938,34 +4882,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>이안네일</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>wendyandj@naver.com</t>
-        </is>
-      </c>
+          <t>정관마일리네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1307-2082</t>
+          <t>0507-1361-4832</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로142번길 11 골든그린빌상가 B동 1층</t>
+          <t>부산광역시 기장군 정관읍 정관로 579 6층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/iann_nail</t>
+          <t>http://pf.kakao.com/_iGXxgC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4986,7 +4926,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4995,13 +4935,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>1176</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R49" t="n">
-        <v>9</v>
+        <v>1201</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5010,17 +4950,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1275481649</t>
+          <t>1181950337</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275481649</t>
+          <t>https://m.place.naver.com/place/1181950337</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5032,29 +4972,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>동생네일</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>umma_89@naver.com</t>
-        </is>
-      </c>
+          <t>더네일킹</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1376-6203</t>
+          <t>0507-1391-3331</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡로 39 301동 1층 106-1호</t>
+          <t>부산광역시 기장군 정관읍 가동1길 11-5 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d.sang_nail</t>
+          <t>http://instagram.com/the_nailking</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5089,13 +5025,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5104,17 +5040,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1061297905</t>
+          <t>1661274406</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061297905</t>
+          <t>https://m.place.naver.com/place/1661274406</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5126,25 +5062,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>신데렐라네일아트</t>
+          <t>동생네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ellie2300@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1376-6203</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 철마면 고촌로28번길 3</t>
+          <t>부산광역시 기장군 정관읍 방곡로 39 301동 1층 106-1호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/d.sang_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5154,7 +5094,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5175,17 +5115,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5194,17 +5134,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1842273793</t>
+          <t>1061297905</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842273793</t>
+          <t>https://m.place.naver.com/place/1061297905</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5216,29 +5156,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>찌니네일</t>
+          <t>김동주네일미학</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>js684177@naver.com</t>
+          <t>muggle4@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1472-5105</t>
+          <t>051-722-3773</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 305 1층</t>
+          <t>부산광역시 기장군 기장읍 차성로326번길 11</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zzini_nail_?igsh=MWRkd3o3amo5MHdkZQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5248,7 +5188,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5269,17 +5209,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5288,17 +5228,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2023205248</t>
+          <t>12939947</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023205248</t>
+          <t>https://m.place.naver.com/place/12939947</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5310,29 +5250,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>남자다운네일 본점</t>
+          <t>보니따뷰티</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>gjbarun@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>051-724-7396</t>
+          <t>051-722-7004</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로288번길 40</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/bonitabeauty_bb</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5342,7 +5282,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5363,17 +5303,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>22</v>
+        <v>437</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>23</v>
+        <v>442</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5382,17 +5322,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1494717985</t>
+          <t>1059332253</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494717985</t>
+          <t>https://m.place.naver.com/place/1059332253</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5404,29 +5344,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>난달라</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h7292uj@naver.com</t>
+          <t>nandala_nail@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>051-724-8232</t>
+          <t>0507-1406-0410</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
+          <t>부산광역시 기장군 정관읍 구연방곡로 120 가화만사성더테라스1차302동108호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h7292uj</t>
+          <t>https://www.instagram.com/nandala_nail.0130</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5441,7 +5381,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5457,17 +5397,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>431</v>
       </c>
       <c r="Q54" t="n">
-        <v>279</v>
+        <v>30</v>
       </c>
       <c r="R54" t="n">
-        <v>283</v>
+        <v>461</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5476,17 +5416,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>16855482</t>
+          <t>1874677609</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16855482</t>
+          <t>https://m.place.naver.com/place/1874677609</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5498,29 +5438,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>하루빛네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>baeyeonjo1@naver.com</t>
-        </is>
-      </c>
+          <t>연하뷰티네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1407-7874</t>
+          <t>0507-1464-4702</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛5로 26 이지더원2차 상가동 109호</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-8 5층 502호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daylight_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5530,7 +5466,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5551,17 +5487,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5570,17 +5506,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1054374644</t>
+          <t>2067837278</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054374644</t>
+          <t>https://m.place.naver.com/place/2067837278</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5592,39 +5528,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일스토리</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>yeju0414@naver.com</t>
-        </is>
-      </c>
+          <t>네일향</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1376-6218</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전로 79 1층 102호</t>
+          <t>부산광역시 기장군 기장읍 차성남로65번길 11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s4fI6Dug</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5640,22 +5568,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5592,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026985488</t>
+          <t>19693133</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026985488</t>
+          <t>https://m.place.naver.com/place/19693133</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5686,34 +5614,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>써니네일</t>
+          <t>727nail</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sunnynails_busan@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1347-9633</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로45번길 1 동부산렉슬 204호</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 324동 108호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Sunny_Nails</t>
+          <t>https://www.instagram.com/727nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5743,13 +5667,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,17 +5682,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1732198376</t>
+          <t>2018352334</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732198376</t>
+          <t>https://m.place.naver.com/place/2018352334</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5780,29 +5704,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>엔포유온네일</t>
+          <t>네일 프롬유</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>paster33@naver.com</t>
+          <t>bojeong2626@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1352-1221</t>
+          <t>0507-1307-0453</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛4로 1 B층 117호</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안 전통상가 1층 A137호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n4u.on_nail</t>
+          <t>https://www.instagram.com/from____you/?igshid=YmMyMTA2M2Y%3D</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5837,13 +5761,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R58" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5852,17 +5776,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2086668706</t>
+          <t>1603411217</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086668706</t>
+          <t>https://m.place.naver.com/place/1603411217</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5874,39 +5798,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일, 살랑</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>blackholecd@naver.com</t>
-        </is>
-      </c>
+          <t>BaRa네일샵</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1347-5811</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동3로 54-4 1층 네일, 살랑</t>
+          <t>부산광역시 기장군 기장읍 차성로288번길 22 1층 BaRa 네일샵</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxfxfxoK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5922,22 +5838,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5946,17 +5862,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1311109904</t>
+          <t>1766863509</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311109904</t>
+          <t>https://m.place.naver.com/place/1766863509</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5968,29 +5884,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H에스테틱</t>
+          <t>네일,만나</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>syuri__@naver.com</t>
+          <t>ehgptn321@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1406-3277</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로182번길 9</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-18</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_h</t>
+          <t>https://open.kakao.com/o/s1IMEHUc</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6016,7 +5928,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6025,13 +5937,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,17 +5952,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1758643778</t>
+          <t>1996364380</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758643778</t>
+          <t>https://m.place.naver.com/place/1996364380</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6062,34 +5974,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에반뷰티</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>evan_b9@naver.com</t>
-        </is>
-      </c>
+          <t>네일세르</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1342-7372</t>
+          <t>0507-1373-5187</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로390번길 15 2층</t>
+          <t>부산광역시 기장군 정관읍 산단4로 153-12 101호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evan_beauty_/</t>
+          <t>http://pf.kakao.com/_iaIZX/chat</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6110,7 +6018,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6119,13 +6027,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>287</v>
+        <v>24</v>
       </c>
       <c r="Q61" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>430</v>
+        <v>26</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,17 +6042,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1626526500</t>
+          <t>2062927983</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626526500</t>
+          <t>https://m.place.naver.com/place/2062927983</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6156,25 +6064,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일앤아이래쉬</t>
+          <t>찌니네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>naileyelashes@naver.com</t>
+          <t>js684177@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1472-5105</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관1로 18 126동 103호</t>
+          <t>부산광역시 기장군 기장읍 차성로 305 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naileyelashes</t>
+          <t>https://www.instagram.com/zzini_nail_?igsh=MWRkd3o3amo5MHdkZQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6189,7 +6101,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6205,17 +6117,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6136,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1000195214</t>
+          <t>2023205248</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000195214</t>
+          <t>https://m.place.naver.com/place/2023205248</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6246,12 +6158,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일코코</t>
+          <t>여우숲네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hydestocker@naver.com</t>
+          <t>hanna7342@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6259,12 +6171,12 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 501-21 1층 102호</t>
+          <t>부산광역시 기장군 기장읍 차성로332번길 14 여우숲 네일</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_coco__jju</t>
+          <t>http://instagram.com/lovely_lail_6604</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6299,13 +6211,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6314,17 +6226,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1109274522</t>
+          <t>1249638908</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109274522</t>
+          <t>https://m.place.naver.com/place/1249638908</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6336,29 +6248,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일 프롬유</t>
+          <t>요니네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bojeong2626@naver.com</t>
+          <t>yoni_nail@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1307-0453</t>
+          <t>0507-1373-7728</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 미래안 전통상가 1층 A137호</t>
+          <t>부산광역시 기장군 기장읍 차성로441번길 7 상가동 104호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/from____you/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6368,7 +6280,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6389,17 +6301,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6408,17 +6320,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1603411217</t>
+          <t>1905392632</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1603411217</t>
+          <t>https://m.place.naver.com/place/1905392632</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6430,39 +6342,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>님프네일</t>
+          <t>H에스테틱</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>syuri__@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1439-0148</t>
+          <t>0507-1406-3277</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성남로55번길 6 1층 님프네일</t>
+          <t>부산광역시 기장군 기장읍 차성동로182번길 9</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/nailby_h</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6487,13 +6399,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R65" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6414,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1168958292</t>
+          <t>1758643778</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168958292</t>
+          <t>https://m.place.naver.com/place/1758643778</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6524,29 +6436,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>모해, 네일앤뷰티</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>정관 아린네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>051-727-0080</t>
+          <t>051-727-1544</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 581 성원프라자 116호 모해, 네일앤뷰티</t>
+          <t>부산광역시 기장군 정관읍 정관로 485 롯데캐슬프라자</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sukyung_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6556,7 +6464,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6577,17 +6485,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6504,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>30839584</t>
+          <t>1312537670</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30839584</t>
+          <t>https://m.place.naver.com/place/1312537670</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6618,34 +6526,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일은빛나게</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>dbswndud9404@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1303-4148</t>
+          <t>0507-1330-4762</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 74 102호</t>
+          <t>부산광역시 기장군 기장읍 차성로322번길 36 1층 영네</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_PtVxcxb/chat</t>
+          <t>https://blog.naver.com/dbswndud9404</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6655,7 +6563,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6666,7 +6574,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6675,13 +6583,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R67" t="n">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6598,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1538578837</t>
+          <t>1527027904</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538578837</t>
+          <t>https://m.place.naver.com/place/1527027904</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6712,25 +6620,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>몽비쥬네일</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>지유네일 기장일광점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1359-9732</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20</t>
+          <t>부산광역시 기장군 일광읍 이화로 7 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailjiyu</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6740,7 +6648,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6761,17 +6669,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6780,17 +6688,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1882702996</t>
+          <t>1722948905</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882702996</t>
+          <t>https://m.place.naver.com/place/1722948905</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6802,29 +6710,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일빛</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>eunbi0888@naver.com</t>
-        </is>
-      </c>
+          <t>톡톡네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1415-3379</t>
+          <t>051-727-3209</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 45 101호 네일빛</t>
+          <t>부산광역시 기장군 정관읍 방곡로 64-9 상가1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bit.kr</t>
+          <t>http://www.instagram.com/sunstory1206</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6859,13 +6763,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
+        <v>615</v>
       </c>
       <c r="R69" t="n">
-        <v>92</v>
+        <v>650</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6874,17 +6778,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1283671318</t>
+          <t>1180143985</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283671318</t>
+          <t>https://m.place.naver.com/place/1180143985</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6896,39 +6800,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>빅토리네일</t>
+          <t>네일봉봉</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kko-maeng@naver.com</t>
+          <t>ye0505@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1330-2859</t>
+          <t>0507-1310-0650</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 5-20 B112호(미래안 전통상가)</t>
+          <t>부산광역시 기장군 기장읍 대청로45번길 19 103호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUIlR3Qe</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6944,22 +6848,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>259</v>
+        <v>2</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6968,17 +6872,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1968808024</t>
+          <t>1569463367</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968808024</t>
+          <t>https://m.place.naver.com/place/1569463367</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6990,29 +6894,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>그녀, 빛나네일</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>usdbaoh24@naver.com</t>
-        </is>
-      </c>
+          <t>리나운 뷰티가든</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1352-6632</t>
+          <t>0507-1442-7669</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관5로 12 상가226동 103호</t>
+          <t>부산광역시 기장군 기장읍 차성로344번길 13 상가동 114호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shesshining_nail?igsh=bDQ4eDh2cjZp</t>
+          <t>https://www.instagram.com/renown_nail7667?igsh=MXhuaDBvYzJ4N3lhZQ==</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7047,13 +6947,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7062,17 +6962,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1874020835</t>
+          <t>1230254733</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874020835</t>
+          <t>https://m.place.naver.com/place/1230254733</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7084,29 +6984,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>정관소노네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>아띠네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1390-5016</t>
+          <t>051-728-3804</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산2길 25-3 로얄하우스 1층</t>
+          <t>부산광역시 기장군 정관읍 정관7로 3</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sono_b.t</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7116,7 +7012,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7137,17 +7033,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7156,17 +7052,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1535038585</t>
+          <t>32434749</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535038585</t>
+          <t>https://m.place.naver.com/place/32434749</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7178,29 +7074,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>디오네일뷰티스튜디오</t>
+          <t>네일리쥬</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jjin0723@naver.com</t>
+          <t>dbdud0328@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1412-2457</t>
+          <t>0507-1384-0540</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관1로 18 이지 더원1차 아파트 상가 125동 B105호</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 213동 B206호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d_o_beauty</t>
+          <t>https://www.instagram.com/nail_leeju</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7235,13 +7131,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="R73" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7250,17 +7146,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1250273367</t>
+          <t>1360272320</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250273367</t>
+          <t>https://m.place.naver.com/place/1360272320</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7272,29 +7168,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>제이밈네일</t>
+          <t>네일J</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jaeny__@naver.com</t>
+          <t>qpqptkfkd7@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1472-4423</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 122 103호</t>
+          <t>부산광역시 기장군 기장읍 차성로 305 1층 네일J</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_mim_nail?igsh=bXdqZmVmcmxwNWcy</t>
+          <t>https://blog.naver.com/qpqptkfkd7</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7309,7 +7201,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7320,7 +7212,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7329,13 +7221,13 @@
         </is>
       </c>
       <c r="P74" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q74" t="n">
         <v>6</v>
       </c>
-      <c r="Q74" t="n">
-        <v>2</v>
-      </c>
       <c r="R74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7236,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1582950449</t>
+          <t>1688859881</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1582950449</t>
+          <t>https://m.place.naver.com/place/1688859881</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7366,24 +7258,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일은맑음</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>kkje38317@naver.com</t>
-        </is>
-      </c>
+          <t>비니네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1412-1149</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛6로 55 1층 네일은맑음</t>
+          <t>부산광역시 기장군 차성동로 92 LG장식</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7426,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7322,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2017375277</t>
+          <t>1734190871</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017375277</t>
+          <t>https://m.place.naver.com/place/1734190871</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7460,25 +7344,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>비니네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>eternel__01@naver.com</t>
-        </is>
-      </c>
+          <t>네일비</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1428-4178</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 차성동로 92 LG장식</t>
+          <t>부산광역시 기장군 기장읍 차성동로87번길 28 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bs_nailbee?igsh=dnI4a2s5ZzJpMW10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7488,7 +7372,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7509,17 +7393,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7528,17 +7412,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1734190871</t>
+          <t>2039408171</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1734190871</t>
+          <t>https://m.place.naver.com/place/2039408171</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7550,29 +7434,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>아이엠네일</t>
+          <t>코델리아진네일뷰티</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>gofhd1215@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1398-5369</t>
+          <t>0507-1316-8137</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 달산길 11 . 101호</t>
+          <t>부산광역시 기장군 기장읍 기장해안로 98 C211호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lm_nail_90</t>
+          <t>https://open.kakao.com/o/sbFNXENb</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7598,7 +7482,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7607,13 +7491,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7622,17 +7506,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1098146719</t>
+          <t>1451145377</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098146719</t>
+          <t>https://m.place.naver.com/place/1451145377</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7644,29 +7528,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>빛나담 뷰티테라스</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>bitnadal_bt@naver.com</t>
-        </is>
-      </c>
+          <t>네일밍</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1388-6656</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 72 4층 401호</t>
+          <t>부산광역시 기장군 정관읍 모전1길 72 . 1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitnadam_bt</t>
+          <t>https://www.instagram.com/nail_ming1226</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7701,13 +7577,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7716,17 +7592,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1729711839</t>
+          <t>1326191176</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729711839</t>
+          <t>https://m.place.naver.com/place/1326191176</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7738,29 +7614,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>뷰티샤네일</t>
+          <t>디오네일뷰티스튜디오</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>daumi0820@naver.com</t>
+          <t>jjin0723@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1354-4413</t>
+          <t>0507-1412-2457</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 213동 b201호</t>
+          <t>부산광역시 기장군 정관읍 정관1로 18 이지 더원1차 아파트 상가 125동 B105호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautychanail</t>
+          <t>https://www.instagram.com/d_o_beauty</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7786,7 +7662,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7795,13 +7671,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R79" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7810,17 +7686,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1573379404</t>
+          <t>1250273367</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573379404</t>
+          <t>https://m.place.naver.com/place/1250273367</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7832,29 +7708,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>연하뷰티네일</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>wldms99888@naver.com</t>
-        </is>
-      </c>
+          <t>임네일</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1464-4702</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-8 5층 502호</t>
+          <t>부산광역시 기장군 정관읍 정관로 563 건물(광장메디컬)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/im_nail_shin</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7864,7 +7732,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7885,17 +7753,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R80" t="n">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7904,17 +7772,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2067837278</t>
+          <t>1205209921</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067837278</t>
+          <t>https://m.place.naver.com/place/1205209921</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7926,29 +7794,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>네일리쥬</t>
+          <t>뷰티샤네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dbdud0328@naver.com</t>
+          <t>daumi0820@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1384-0540</t>
+          <t>0507-1354-4413</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 213동 B206호</t>
+          <t>부산광역시 기장군 정관읍 정관2로 9 213동 b201호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_leeju</t>
+          <t>https://www.instagram.com/beautychanail</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7974,7 +7842,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7983,13 +7851,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="Q81" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="R81" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7998,17 +7866,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1360272320</t>
+          <t>1573379404</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1360272320</t>
+          <t>https://m.place.naver.com/place/1573379404</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8020,29 +7888,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일더무드 부산정관점</t>
+          <t>손끄치스치다</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>innazzang-@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1434-9030</t>
+          <t>0507-1432-1235</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 9 상가 B209호</t>
+          <t>부산광역시 기장군 정관읍 정관로 350 . 323동 107호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/0701_a_reum/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8052,7 +7920,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8073,17 +7941,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="Q82" t="n">
         <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>142</v>
+        <v>5</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8092,17 +7960,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1467606881</t>
+          <t>38479059</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467606881</t>
+          <t>https://m.place.naver.com/place/38479059</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8114,29 +7982,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>보니따뷰티</t>
+          <t>빅토리네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>gjbarun@naver.com</t>
+          <t>kko-maeng@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>051-722-7004</t>
+          <t>0507-1330-2859</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 5</t>
+          <t>부산광역시 기장군 정관읍 정관6로 5-20 B112호(미래안 전통상가)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>http://instagram.com/bonitabeauty_bb</t>
+          <t>https://open.kakao.com/o/sUIlR3Qe</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8162,7 +8030,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8171,13 +8039,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>437</v>
+        <v>256</v>
       </c>
       <c r="Q83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R83" t="n">
-        <v>442</v>
+        <v>260</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8186,17 +8054,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1059332253</t>
+          <t>1968808024</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059332253</t>
+          <t>https://m.place.naver.com/place/1968808024</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8208,24 +8076,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>리네일</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>dlwjddo7053@naver.com</t>
-        </is>
-      </c>
+          <t>네일은맑음</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1362-5752</t>
+          <t>0507-1412-1149</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 가동2길 24-7 리네일</t>
+          <t>부산광역시 기장군 일광읍 해빛6로 55 1층 네일은맑음</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8265,13 +8129,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8280,17 +8144,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1105532713</t>
+          <t>2017375277</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105532713</t>
+          <t>https://m.place.naver.com/place/2017375277</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8302,29 +8166,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>즐거운네일</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>mneilacademy@naver.com</t>
-        </is>
-      </c>
+          <t>어게인뷰티</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0507-1433-3022</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관덕산길 80 파스텔라상가 1층 6호 즐거운네일</t>
+          <t>부산광역시 기장군 정관읍 모전로 78-1 1층 101호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/again_b.t</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8334,7 +8190,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8355,17 +8211,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>563</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>576</v>
+        <v>5</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8374,17 +8230,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1490033165</t>
+          <t>1843319378</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490033165</t>
+          <t>https://m.place.naver.com/place/1843319378</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8396,24 +8252,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>보니네일&amp;좌훈카페</t>
+          <t>네일홀릭</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>minmin0319@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>051-727-1632</t>
+          <t>0507-1362-0848</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관중앙로 58</t>
+          <t>부산광역시 기장군 정관읍 달산길 22-11 1층 네일홀릭</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8456,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8468,17 +8324,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>34624678</t>
+          <t>1461860750</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34624678</t>
+          <t>https://m.place.naver.com/place/1461860750</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8490,25 +8346,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>마이네일숍</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>hanzzang25@naver.com</t>
-        </is>
-      </c>
+          <t>검은고양이네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1320-6761</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 장안읍 길천길 15 1층 101호</t>
+          <t>부산광역시 기장군 정관읍 방곡로 29</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mynailshop_</t>
+          <t>https://blackcat.mqpon.co.kr/</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8539,17 +8395,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R87" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8558,17 +8414,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1576268118</t>
+          <t>1921074769</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576268118</t>
+          <t>https://m.place.naver.com/place/1921074769</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8580,29 +8436,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>리나운 뷰티가든</t>
+          <t>빈s magic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>wldms99888@naver.com</t>
+          <t>overcome6@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1442-7669</t>
+          <t>0507-1359-6914</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로344번길 13 상가동 114호</t>
+          <t>부산광역시 기장군 기장읍 차성남로 63 1층 빈s magic</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/renown_nail7667?igsh=MXhuaDBvYzJ4N3lhZQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8612,7 +8468,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8633,17 +8489,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8652,17 +8508,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1230254733</t>
+          <t>1527971991</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230254733</t>
+          <t>https://m.place.naver.com/place/1527971991</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8674,29 +8530,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>김동주네일미학</t>
+          <t>베스타네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>muggle4@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>051-722-3773</t>
+          <t>0507-1398-1666</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로326번길 11</t>
+          <t>부산광역시 기장군 일광읍 해송4로 21 일광프라자 3층 304호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/me/vesta</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8706,7 +8562,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8722,22 +8578,22 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8746,17 +8602,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>12939947</t>
+          <t>1527088754</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12939947</t>
+          <t>https://m.place.naver.com/place/1527088754</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8768,25 +8624,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>임네일</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>hj_zzang@naver.com</t>
-        </is>
-      </c>
+          <t>모해, 네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>051-727-0080</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 563 건물(광장메디컬)</t>
+          <t>부산광역시 기장군 정관읍 정관로 581 성원프라자 116호 모해, 네일앤뷰티</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/im_nail_shin</t>
+          <t>https://www.instagram.com/sukyung_nail</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8821,13 +8677,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="Q90" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8836,17 +8692,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1205209921</t>
+          <t>30839584</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205209921</t>
+          <t>https://m.place.naver.com/place/30839584</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8858,35 +8714,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>수진네일아트</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>linnii@naver.com</t>
-        </is>
-      </c>
+          <t>어썸네일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1371-2638</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
+          <t>부산광역시 기장군 정관읍 모전3길 43 102호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xkXxcqX/friend</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8902,22 +8758,22 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="R91" t="n">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8926,17 +8782,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1769136676</t>
+          <t>2043055430</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769136676</t>
+          <t>https://m.place.naver.com/place/2043055430</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8948,29 +8804,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>네일,은</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>minukyung@naver.com</t>
-        </is>
-      </c>
+          <t>에이치네일</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1373-0854</t>
+          <t>0507-1308-6632</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 383 대성타워빌딩 B103호</t>
+          <t>부산광역시 기장군 정관읍 구연방곡로 10 정문상가104호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.eun_/profilecard/?igsh=MXhid2VxMzVrdmMwYQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8980,7 +8832,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9001,17 +8853,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9020,17 +8872,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1799936115</t>
+          <t>1252239066</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799936115</t>
+          <t>https://m.place.naver.com/place/1252239066</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9042,25 +8894,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일밍</t>
+          <t>어니st네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ksk98815@naver.com</t>
+          <t>audwn082@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1419-2720</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 72 . 1층</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 122 디바인스퀘어 상가 1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ming1226</t>
+          <t>https://pf.kakao.com/_UxdxlxlG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9075,7 +8931,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9086,7 +8942,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9095,13 +8951,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9110,17 +8966,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1326191176</t>
+          <t>1544355473</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326191176</t>
+          <t>https://m.place.naver.com/place/1544355473</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9132,34 +8988,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>정관마일리네일</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>tinda_com@naver.com</t>
+          <t>rkohsje@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1361-4832</t>
+          <t>0507-1376-6218</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 579 6층</t>
+          <t>부산광역시 기장군 정관읍 모전로 79 1층 102호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_iGXxgC</t>
+          <t>https://open.kakao.com/o/s4fI6Dug</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9189,13 +9045,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1176</v>
+        <v>12</v>
       </c>
       <c r="Q94" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>1201</v>
+        <v>13</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9204,17 +9060,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1181950337</t>
+          <t>2026985488</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181950337</t>
+          <t>https://m.place.naver.com/place/2026985488</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9226,29 +9082,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>제이오스카네일 기장일광점</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>joscar_nail@naver.com</t>
+          <t>h7292uj@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1406-5802</t>
+          <t>051-724-8232</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 43 제이오스카 네일</t>
+          <t>부산광역시 기장군 기장읍 차성로436번길 8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.oscar_nail</t>
+          <t>https://blog.naver.com/h7292uj</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9263,7 +9119,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9279,17 +9135,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="Q95" t="n">
-        <v>32</v>
+        <v>279</v>
       </c>
       <c r="R95" t="n">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,17 +9154,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1177930986</t>
+          <t>16855482</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177930986</t>
+          <t>https://m.place.naver.com/place/16855482</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9320,29 +9176,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>정숙한야시</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>dbswndud9404@naver.com</t>
+          <t>wldms99888@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>0507-1330-4762</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로322번길 36 1층 영네</t>
+          <t>부산광역시 기장군 기장읍 차성로441번길 7</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dbswndud9404</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9352,12 +9204,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9373,17 +9225,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9392,17 +9244,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1527027904</t>
+          <t>1074484941</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527027904</t>
+          <t>https://m.place.naver.com/place/1074484941</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9414,12 +9266,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>어게인뷰티</t>
+          <t>네일앤아이래쉬</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>daliboni@naver.com</t>
+          <t>naileyelashes@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -9427,17 +9279,17 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전로 78-1 1층 101호</t>
+          <t>부산광역시 기장군 정관읍 정관1로 18 126동 103호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/again_b.t</t>
+          <t>https://blog.naver.com/naileyelashes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9463,17 +9315,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q97" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9482,17 +9334,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1843319378</t>
+          <t>1000195214</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843319378</t>
+          <t>https://m.place.naver.com/place/1000195214</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9504,29 +9356,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>톡톡네일</t>
+          <t>제이오스카네일 기장일광점</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ekgnlzz@naver.com</t>
+          <t>joscar_nail@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>051-727-3209</t>
+          <t>0507-1406-5802</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 방곡로 64-9 상가1층</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 43 제이오스카 네일</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sunstory1206</t>
+          <t>https://www.instagram.com/j.oscar_nail</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9561,13 +9413,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="Q98" t="n">
-        <v>615</v>
+        <v>32</v>
       </c>
       <c r="R98" t="n">
-        <v>650</v>
+        <v>202</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9576,17 +9428,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1180143985</t>
+          <t>1177930986</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180143985</t>
+          <t>https://m.place.naver.com/place/1177930986</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9598,39 +9450,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>어니st네일</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>audwn082@naver.com</t>
-        </is>
-      </c>
+          <t>보니네일&amp;좌훈카페</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1419-2720</t>
+          <t>051-727-1632</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 122 디바인스퀘어 상가 1층</t>
+          <t>부산광역시 기장군 정관읍 정관중앙로 58</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_UxdxlxlG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9646,22 +9494,22 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9670,17 +9518,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1544355473</t>
+          <t>34624678</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544355473</t>
+          <t>https://m.place.naver.com/place/34624678</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9749,13 +9597,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q100" t="n">
         <v>9</v>
       </c>
       <c r="R100" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9774,7 +9622,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9712,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
